--- a/data_raw/smelt/SLS catch update12.30.25.xlsx
+++ b/data_raw/smelt/SLS catch update12.30.25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\NativeFish\Data Reporting\SLS Catch Summaries\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/lmccormick_usbr_gov/Documents/Documents/Research/R/samt_smt_assessments/data_raw/smelt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDA06FB-3F38-460B-B362-E9CE7B168ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{CDDA06FB-3F38-460B-B362-E9CE7B168ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89F1EA17-9923-4310-9FA9-CDA7695207D8}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E318DA66-929E-4160-AE8F-A3EAE62CC340}"/>
+    <workbookView xWindow="12564" yWindow="-15624" windowWidth="26160" windowHeight="13896" xr2:uid="{E318DA66-929E-4160-AE8F-A3EAE62CC340}"/>
   </bookViews>
   <sheets>
     <sheet name="Survey 12" sheetId="10" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="29">
   <si>
     <t>Year</t>
   </si>
@@ -82,30 +82,6 @@
   </si>
   <si>
     <t>Turbidity (FNU)</t>
-  </si>
-  <si>
-    <t>San pablo</t>
-  </si>
-  <si>
-    <t>Napa River</t>
-  </si>
-  <si>
-    <t>carquinez strait</t>
-  </si>
-  <si>
-    <t>Suisun bay and Marsh</t>
-  </si>
-  <si>
-    <t>Confluence</t>
-  </si>
-  <si>
-    <t>Sac River system</t>
-  </si>
-  <si>
-    <t>809+812</t>
-  </si>
-  <si>
-    <t>Other Central &amp; south</t>
   </si>
   <si>
     <t xml:space="preserve">SWP ITP </t>
@@ -1357,25 +1333,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P75"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.42578125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" style="23" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="61" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" style="23" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" style="23" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="23" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="23" customWidth="1"/>
-    <col min="9" max="9" width="6.85546875" style="23" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" style="56" customWidth="1"/>
-    <col min="11" max="12" width="6.42578125" style="23" customWidth="1"/>
-    <col min="13" max="13" width="6.42578125" style="62" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" style="23" customWidth="1"/>
-    <col min="15" max="15" width="9.5703125" customWidth="1"/>
-    <col min="16" max="16" width="2.5703125" customWidth="1"/>
+    <col min="1" max="2" width="6.44140625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" style="23" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="61" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="6.5546875" style="23" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" style="23" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" style="23" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" style="56" customWidth="1"/>
+    <col min="11" max="12" width="6.44140625" style="23" customWidth="1"/>
+    <col min="13" max="13" width="6.44140625" style="62" customWidth="1"/>
+    <col min="14" max="14" width="9.88671875" style="23" customWidth="1"/>
+    <col min="15" max="15" width="9.5546875" customWidth="1"/>
+    <col min="16" max="16" width="2.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="59" t="s">
         <v>0</v>
       </c>
@@ -1421,7 +1397,7 @@
       <c r="O1" s="15"/>
       <c r="P1" s="14"/>
     </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="52">
         <v>2026</v>
       </c>
@@ -1441,14 +1417,14 @@
         <v>71</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I2" s="24"/>
       <c r="J2" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
@@ -1457,7 +1433,7 @@
       <c r="O2" s="15"/>
       <c r="P2" s="14"/>
     </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="53">
         <f>A2</f>
         <v>2026</v>
@@ -1479,14 +1455,14 @@
         <v>70</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I3" s="25"/>
       <c r="J3" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
@@ -1495,7 +1471,7 @@
       <c r="O3" s="15"/>
       <c r="P3" s="14"/>
     </row>
-    <row r="4" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="53">
         <f t="shared" ref="A4:A60" si="0">A3</f>
         <v>2026</v>
@@ -1517,14 +1493,14 @@
         <v>80</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I4" s="25"/>
       <c r="J4" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
@@ -1533,7 +1509,7 @@
       <c r="O4" s="15"/>
       <c r="P4" s="14"/>
     </row>
-    <row r="5" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -1555,14 +1531,14 @@
         <v>47</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I5" s="24"/>
       <c r="J5" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
@@ -1571,7 +1547,7 @@
       <c r="O5" s="15"/>
       <c r="P5" s="14"/>
     </row>
-    <row r="6" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -1593,14 +1569,14 @@
         <v>70</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I6" s="25"/>
       <c r="J6" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
@@ -1609,7 +1585,7 @@
       <c r="O6" s="15"/>
       <c r="P6" s="14"/>
     </row>
-    <row r="7" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -1631,14 +1607,14 @@
         <v>80</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I7" s="25"/>
       <c r="J7" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
@@ -1647,7 +1623,7 @@
       <c r="O7" s="15"/>
       <c r="P7" s="14"/>
     </row>
-    <row r="8" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -1669,14 +1645,14 @@
         <v>50</v>
       </c>
       <c r="G8" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I8" s="25"/>
       <c r="J8" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
@@ -1685,7 +1661,7 @@
       <c r="O8" s="15"/>
       <c r="P8" s="14"/>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -1707,14 +1683,14 @@
         <v>40</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I9" s="25"/>
       <c r="J9" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
@@ -1723,7 +1699,7 @@
       <c r="O9" s="15"/>
       <c r="P9" s="14"/>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -1745,14 +1721,14 @@
         <v>80</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I10" s="25"/>
       <c r="J10" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
@@ -1761,7 +1737,7 @@
       <c r="O10" s="15"/>
       <c r="P10" s="14"/>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -1783,14 +1759,14 @@
         <v>62</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I11" s="25"/>
       <c r="J11" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
@@ -1799,7 +1775,7 @@
       <c r="O11" s="15"/>
       <c r="P11" s="14"/>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -1821,14 +1797,14 @@
         <v>110</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I12" s="24"/>
       <c r="J12" s="9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
@@ -1837,7 +1813,7 @@
       <c r="O12" s="15"/>
       <c r="P12" s="14"/>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -1859,14 +1835,14 @@
         <v>70</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I13" s="25"/>
       <c r="J13" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
@@ -1875,7 +1851,7 @@
       <c r="O13" s="15"/>
       <c r="P13" s="14"/>
     </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -1897,14 +1873,14 @@
         <v>56</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I14" s="25"/>
       <c r="J14" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -1913,7 +1889,7 @@
       <c r="O14" s="15"/>
       <c r="P14" s="14"/>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -1935,14 +1911,14 @@
         <v>50</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I15" s="25"/>
       <c r="J15" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
@@ -1951,7 +1927,7 @@
       <c r="O15" s="15"/>
       <c r="P15" s="14"/>
     </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -1973,14 +1949,14 @@
         <v>56</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I16" s="26"/>
       <c r="J16" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -1989,7 +1965,7 @@
       <c r="O16" s="15"/>
       <c r="P16" s="14"/>
     </row>
-    <row r="17" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2011,14 +1987,14 @@
         <v>65</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I17" s="26"/>
       <c r="J17" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -2027,7 +2003,7 @@
       <c r="O17" s="15"/>
       <c r="P17" s="14"/>
     </row>
-    <row r="18" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2049,14 +2025,14 @@
         <v>57</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I18" s="26"/>
       <c r="J18" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -2065,7 +2041,7 @@
       <c r="O18" s="15"/>
       <c r="P18" s="14"/>
     </row>
-    <row r="19" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2087,14 +2063,14 @@
         <v>74</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I19" s="26"/>
       <c r="J19" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -2103,7 +2079,7 @@
       <c r="O19" s="15"/>
       <c r="P19" s="14"/>
     </row>
-    <row r="20" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2125,14 +2101,14 @@
         <v>83</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I20" s="26"/>
       <c r="J20" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -2141,7 +2117,7 @@
       <c r="O20" s="15"/>
       <c r="P20" s="14"/>
     </row>
-    <row r="21" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2163,14 +2139,14 @@
         <v>140</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I21" s="26"/>
       <c r="J21" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -2179,7 +2155,7 @@
       <c r="O21" s="15"/>
       <c r="P21" s="14"/>
     </row>
-    <row r="22" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2201,14 +2177,14 @@
         <v>124</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I22" s="26"/>
       <c r="J22" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -2217,7 +2193,7 @@
       <c r="O22" s="15"/>
       <c r="P22" s="14"/>
     </row>
-    <row r="23" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2239,14 +2215,14 @@
         <v>120</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I23" s="26"/>
       <c r="J23" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -2255,7 +2231,7 @@
       <c r="O23" s="15"/>
       <c r="P23" s="14"/>
     </row>
-    <row r="24" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2277,14 +2253,14 @@
         <v>86</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I24" s="26"/>
       <c r="J24" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -2293,7 +2269,7 @@
       <c r="O24" s="15"/>
       <c r="P24" s="14"/>
     </row>
-    <row r="25" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2315,14 +2291,14 @@
         <v>70</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I25" s="26"/>
       <c r="J25" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -2331,7 +2307,7 @@
       <c r="O25" s="15"/>
       <c r="P25" s="14"/>
     </row>
-    <row r="26" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2353,14 +2329,14 @@
         <v>57</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I26" s="26"/>
       <c r="J26" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -2369,7 +2345,7 @@
       <c r="O26" s="15"/>
       <c r="P26" s="14"/>
     </row>
-    <row r="27" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2391,14 +2367,14 @@
         <v>55</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I27" s="26"/>
       <c r="J27" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -2407,7 +2383,7 @@
       <c r="O27" s="15"/>
       <c r="P27" s="14"/>
     </row>
-    <row r="28" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2429,14 +2405,14 @@
         <v>73</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I28" s="26"/>
       <c r="J28" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -2445,7 +2421,7 @@
       <c r="O28" s="15"/>
       <c r="P28" s="14"/>
     </row>
-    <row r="29" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2467,14 +2443,14 @@
         <v>43</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I29" s="26"/>
       <c r="J29" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -2483,7 +2459,7 @@
       <c r="O29" s="15"/>
       <c r="P29" s="14"/>
     </row>
-    <row r="30" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2505,14 +2481,14 @@
         <v>52</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I30" s="26"/>
       <c r="J30" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -2521,7 +2497,7 @@
       <c r="O30" s="15"/>
       <c r="P30" s="14"/>
     </row>
-    <row r="31" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2543,14 +2519,14 @@
         <v>45</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I31" s="39"/>
       <c r="J31" s="55" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -2559,7 +2535,7 @@
       <c r="O31" s="15"/>
       <c r="P31" s="14"/>
     </row>
-    <row r="32" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2581,14 +2557,14 @@
         <v>79</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I32" s="39"/>
       <c r="J32" s="56" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -2597,7 +2573,7 @@
       <c r="O32" s="14"/>
       <c r="P32" s="14"/>
     </row>
-    <row r="33" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2619,14 +2595,14 @@
         <v>38</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I33" s="26"/>
       <c r="J33" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -2635,7 +2611,7 @@
       <c r="O33" s="15"/>
       <c r="P33" s="14"/>
     </row>
-    <row r="34" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2657,14 +2633,14 @@
         <v>62</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I34" s="26"/>
       <c r="J34" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -2673,7 +2649,7 @@
       <c r="O34" s="15"/>
       <c r="P34" s="14"/>
     </row>
-    <row r="35" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2695,14 +2671,14 @@
         <v>30</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I35" s="26"/>
       <c r="J35" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -2711,7 +2687,7 @@
       <c r="O35" s="15"/>
       <c r="P35" s="14"/>
     </row>
-    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2733,14 +2709,14 @@
         <v>28</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I36" s="26"/>
       <c r="J36" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -2749,7 +2725,7 @@
       <c r="O36" s="14"/>
       <c r="P36" s="14"/>
     </row>
-    <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2771,14 +2747,14 @@
         <v>25</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I37" s="39"/>
       <c r="J37" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -2787,7 +2763,7 @@
       <c r="O37" s="14"/>
       <c r="P37" s="14"/>
     </row>
-    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2809,14 +2785,14 @@
         <v>45</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I38" s="39"/>
       <c r="J38" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -2825,7 +2801,7 @@
       <c r="O38" s="14"/>
       <c r="P38" s="14"/>
     </row>
-    <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2847,14 +2823,14 @@
         <v>56</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I39" s="26"/>
       <c r="J39" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -2862,7 +2838,7 @@
       <c r="N39" s="32"/>
       <c r="P39" s="14"/>
     </row>
-    <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2884,14 +2860,14 @@
         <v>39</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I40" s="26"/>
       <c r="J40" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -2900,7 +2876,7 @@
       <c r="O40" s="14"/>
       <c r="P40" s="14"/>
     </row>
-    <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2922,14 +2898,14 @@
         <v>85</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I41" s="26"/>
       <c r="J41" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -2938,7 +2914,7 @@
       <c r="O41" s="14"/>
       <c r="P41" s="14"/>
     </row>
-    <row r="42" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2960,14 +2936,14 @@
         <v>36</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I42" s="26"/>
       <c r="J42" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -2976,7 +2952,7 @@
       <c r="O42" s="14"/>
       <c r="P42" s="14"/>
     </row>
-    <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -2998,14 +2974,14 @@
         <v>68</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I43" s="26"/>
       <c r="J43" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -3014,7 +2990,7 @@
       <c r="O43" s="14"/>
       <c r="P43" s="14"/>
     </row>
-    <row r="44" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3036,14 +3012,14 @@
         <v>145</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I44" s="26"/>
       <c r="J44" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -3052,7 +3028,7 @@
       <c r="O44" s="14"/>
       <c r="P44" s="14"/>
     </row>
-    <row r="45" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3074,14 +3050,14 @@
         <v>115</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I45" s="26"/>
       <c r="J45" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -3090,7 +3066,7 @@
       <c r="O45" s="78"/>
       <c r="P45" s="14"/>
     </row>
-    <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3112,14 +3088,14 @@
         <v>120</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I46" s="26"/>
       <c r="J46" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -3128,7 +3104,7 @@
       <c r="O46" s="14"/>
       <c r="P46" s="14"/>
     </row>
-    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3150,14 +3126,14 @@
         <v>87</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I47" s="26"/>
       <c r="J47" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -3166,7 +3142,7 @@
       <c r="O47" s="7"/>
       <c r="P47" s="14"/>
     </row>
-    <row r="48" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3188,14 +3164,14 @@
         <v>77</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I48" s="26"/>
       <c r="J48" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -3204,7 +3180,7 @@
       <c r="O48" s="14"/>
       <c r="P48" s="14"/>
     </row>
-    <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="75">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3226,25 +3202,25 @@
         <v>122</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I49" s="27"/>
       <c r="J49" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="30"/>
       <c r="N49" s="33"/>
       <c r="O49" s="85" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="P49" s="14"/>
     </row>
-    <row r="50" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="75">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3266,14 +3242,14 @@
         <v>109</v>
       </c>
       <c r="G50" s="38" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I50" s="27"/>
       <c r="J50" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
@@ -3282,7 +3258,7 @@
       <c r="O50" s="86"/>
       <c r="P50" s="14"/>
     </row>
-    <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3304,14 +3280,14 @@
         <v>114</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I51" s="26"/>
       <c r="J51" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -3320,7 +3296,7 @@
       <c r="O51" s="67"/>
       <c r="P51" s="14"/>
     </row>
-    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3342,14 +3318,14 @@
         <v>132</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -3358,7 +3334,7 @@
       <c r="O52" s="67"/>
       <c r="P52" s="14"/>
     </row>
-    <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3380,14 +3356,14 @@
         <v>200</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -3396,7 +3372,7 @@
       <c r="O53" s="67"/>
       <c r="P53" s="14"/>
     </row>
-    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3416,14 +3392,14 @@
         <v>141</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -3432,7 +3408,7 @@
       <c r="O54" s="67"/>
       <c r="P54" s="14"/>
     </row>
-    <row r="55" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3454,14 +3430,14 @@
         <v>200</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -3470,7 +3446,7 @@
       <c r="O55" s="67"/>
       <c r="P55" s="14"/>
     </row>
-    <row r="56" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3492,14 +3468,14 @@
         <v>151</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -3508,7 +3484,7 @@
       <c r="O56" s="67"/>
       <c r="P56" s="14"/>
     </row>
-    <row r="57" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3528,14 +3504,14 @@
         <v>200</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -3544,7 +3520,7 @@
       <c r="O57" s="67"/>
       <c r="P57" s="14"/>
     </row>
-    <row r="58" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3564,14 +3540,14 @@
         <v>200</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -3580,7 +3556,7 @@
       <c r="O58" s="67"/>
       <c r="P58" s="14"/>
     </row>
-    <row r="59" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3602,14 +3578,14 @@
         <v>200</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -3618,7 +3594,7 @@
       <c r="O59" s="67"/>
       <c r="P59" s="14"/>
     </row>
-    <row r="60" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="76">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -3638,14 +3614,14 @@
         <v>151</v>
       </c>
       <c r="G60" s="72" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H60" s="68" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I60" s="71"/>
       <c r="J60" s="68" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K60" s="68"/>
       <c r="L60" s="68"/>
@@ -3654,9 +3630,9 @@
       <c r="O60" s="67"/>
       <c r="P60" s="14"/>
     </row>
-    <row r="61" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="80" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B61" s="81"/>
       <c r="C61" s="81"/>
@@ -3673,9 +3649,9 @@
       <c r="N61" s="6"/>
       <c r="O61" s="14"/>
     </row>
-    <row r="62" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="80" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B62" s="82"/>
       <c r="C62" s="82"/>
@@ -3692,9 +3668,9 @@
       <c r="N62" s="28"/>
       <c r="O62" s="14"/>
     </row>
-    <row r="63" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="80" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B63" s="82"/>
       <c r="C63" s="82"/>
@@ -3711,9 +3687,9 @@
       <c r="N63" s="36"/>
       <c r="O63" s="14"/>
     </row>
-    <row r="64" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="83" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B64" s="84"/>
       <c r="C64" s="84"/>
@@ -3730,158 +3706,126 @@
       <c r="N64" s="36"/>
       <c r="O64" s="14"/>
     </row>
-    <row r="65" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F65" s="22">
-        <f>AVERAGE(F49:F60)</f>
-        <v>160</v>
-      </c>
-      <c r="I65" s="21">
-        <f>SUM(I2:I60)</f>
-        <v>0</v>
-      </c>
-      <c r="N65" s="63">
-        <f>SUM(N2:N60)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H67" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="64">
-        <f>SUM(I2:I13)</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="M67" s="58">
-        <f t="shared" ref="M67:M75" si="2">I67-K67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H68" s="66" t="s">
-        <v>15</v>
-      </c>
-      <c r="I68" s="64">
-        <f>SUM(I15:I23)</f>
-        <v>0</v>
-      </c>
-      <c r="J68" s="77" t="s">
-        <v>15</v>
-      </c>
-      <c r="M68" s="58">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H69" s="66" t="s">
-        <v>16</v>
-      </c>
-      <c r="I69" s="64">
-        <f>SUM(I24+I25+I26+I14)</f>
-        <v>0</v>
-      </c>
-      <c r="J69" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="M69" s="58">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H70" s="66" t="s">
-        <v>17</v>
-      </c>
-      <c r="I70" s="64">
-        <f>SUM(I27+I28+I29+I30+I33+I35+I36+I37+I38)</f>
-        <v>0</v>
-      </c>
-      <c r="J70" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="M70" s="58">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H71" s="66" t="s">
-        <v>18</v>
-      </c>
-      <c r="I71" s="64">
-        <f>SUM(I31+I32+I34+I47+I48)</f>
-        <v>0</v>
-      </c>
-      <c r="J71" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="M71" s="58">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H72" s="66" t="s">
-        <v>19</v>
-      </c>
-      <c r="I72" s="64">
-        <f>SUM(I39:I46)</f>
-        <v>0</v>
-      </c>
-      <c r="J72" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="M72" s="58">
-        <f>I72-K72</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H73" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="I73" s="64">
-        <f>SUM(I51:I60)</f>
-        <v>0</v>
-      </c>
-      <c r="J73" s="77" t="s">
-        <v>21</v>
-      </c>
-      <c r="M73" s="58">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H74" s="66" t="s">
-        <v>20</v>
-      </c>
-      <c r="I74" s="64">
-        <f>SUM(I49:I50)</f>
-        <v>0</v>
-      </c>
-      <c r="J74" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="M74" s="58">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H75" s="65"/>
-      <c r="I75" s="64">
-        <f>SUM(I67:I74)</f>
-        <v>0</v>
-      </c>
-      <c r="M75" s="58">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+    <row r="65" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="H65"/>
+      <c r="I65"/>
+      <c r="J65"/>
+      <c r="K65"/>
+      <c r="L65"/>
+      <c r="M65"/>
+      <c r="N65"/>
+    </row>
+    <row r="66" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F66"/>
+      <c r="G66"/>
+      <c r="H66"/>
+      <c r="I66"/>
+      <c r="J66"/>
+      <c r="K66"/>
+      <c r="L66"/>
+      <c r="M66"/>
+      <c r="N66"/>
+    </row>
+    <row r="67" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F67"/>
+      <c r="G67"/>
+      <c r="H67"/>
+      <c r="I67"/>
+      <c r="J67"/>
+      <c r="K67"/>
+      <c r="L67"/>
+      <c r="M67"/>
+      <c r="N67"/>
+    </row>
+    <row r="68" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F68"/>
+      <c r="G68"/>
+      <c r="H68"/>
+      <c r="I68"/>
+      <c r="J68"/>
+      <c r="K68"/>
+      <c r="L68"/>
+      <c r="M68"/>
+      <c r="N68"/>
+    </row>
+    <row r="69" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F69"/>
+      <c r="G69"/>
+      <c r="H69"/>
+      <c r="I69"/>
+      <c r="J69"/>
+      <c r="K69"/>
+      <c r="L69"/>
+      <c r="M69"/>
+      <c r="N69"/>
+    </row>
+    <row r="70" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F70"/>
+      <c r="G70"/>
+      <c r="H70"/>
+      <c r="I70"/>
+      <c r="J70"/>
+      <c r="K70"/>
+      <c r="L70"/>
+      <c r="M70"/>
+      <c r="N70"/>
+    </row>
+    <row r="71" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F71"/>
+      <c r="G71"/>
+      <c r="H71"/>
+      <c r="I71"/>
+      <c r="J71"/>
+      <c r="K71"/>
+      <c r="L71"/>
+      <c r="M71"/>
+      <c r="N71"/>
+    </row>
+    <row r="72" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F72"/>
+      <c r="G72"/>
+      <c r="H72"/>
+      <c r="I72"/>
+      <c r="J72"/>
+      <c r="K72"/>
+      <c r="L72"/>
+      <c r="M72"/>
+      <c r="N72"/>
+    </row>
+    <row r="73" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F73"/>
+      <c r="G73"/>
+      <c r="H73"/>
+      <c r="I73"/>
+      <c r="J73"/>
+      <c r="K73"/>
+      <c r="L73"/>
+      <c r="M73"/>
+      <c r="N73"/>
+    </row>
+    <row r="74" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F74"/>
+      <c r="G74"/>
+      <c r="H74"/>
+      <c r="I74"/>
+      <c r="J74"/>
+      <c r="K74"/>
+      <c r="L74"/>
+      <c r="M74"/>
+      <c r="N74"/>
+    </row>
+    <row r="75" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F75"/>
+      <c r="G75"/>
+      <c r="H75"/>
+      <c r="I75"/>
+      <c r="J75"/>
+      <c r="K75"/>
+      <c r="L75"/>
+      <c r="M75"/>
+      <c r="N75"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3909,25 +3853,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P75"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.42578125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" style="23" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="61" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" style="23" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" style="23" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="23" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="23" customWidth="1"/>
-    <col min="9" max="9" width="6.85546875" style="23" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" style="56" customWidth="1"/>
-    <col min="11" max="12" width="6.42578125" style="23" customWidth="1"/>
-    <col min="13" max="13" width="6.42578125" style="62" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" style="23" customWidth="1"/>
-    <col min="15" max="15" width="9.5703125" customWidth="1"/>
-    <col min="16" max="16" width="2.5703125" customWidth="1"/>
+    <col min="1" max="2" width="6.44140625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" style="23" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="61" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="6.5546875" style="23" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" style="23" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" style="23" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" style="56" customWidth="1"/>
+    <col min="11" max="12" width="6.44140625" style="23" customWidth="1"/>
+    <col min="13" max="13" width="6.44140625" style="62" customWidth="1"/>
+    <col min="14" max="14" width="9.88671875" style="23" customWidth="1"/>
+    <col min="15" max="15" width="9.5546875" customWidth="1"/>
+    <col min="16" max="16" width="2.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="59" t="s">
         <v>0</v>
       </c>
@@ -3973,7 +3917,7 @@
       <c r="O1" s="15"/>
       <c r="P1" s="14"/>
     </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="52">
         <v>2026</v>
       </c>
@@ -3993,14 +3937,14 @@
         <v>62</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I2" s="24"/>
       <c r="J2" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
@@ -4009,7 +3953,7 @@
       <c r="O2" s="15"/>
       <c r="P2" s="14"/>
     </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="53">
         <f>A2</f>
         <v>2026</v>
@@ -4031,14 +3975,14 @@
         <v>81</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I3" s="25"/>
       <c r="J3" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
@@ -4047,7 +3991,7 @@
       <c r="O3" s="15"/>
       <c r="P3" s="14"/>
     </row>
-    <row r="4" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="53">
         <f t="shared" ref="A4:B60" si="0">A3</f>
         <v>2026</v>
@@ -4069,14 +4013,14 @@
         <v>90</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I4" s="25"/>
       <c r="J4" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
@@ -4085,7 +4029,7 @@
       <c r="O4" s="15"/>
       <c r="P4" s="14"/>
     </row>
-    <row r="5" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4107,14 +4051,14 @@
         <v>57</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I5" s="24"/>
       <c r="J5" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
@@ -4123,7 +4067,7 @@
       <c r="O5" s="15"/>
       <c r="P5" s="14"/>
     </row>
-    <row r="6" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4145,14 +4089,14 @@
         <v>67</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I6" s="25"/>
       <c r="J6" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
@@ -4161,7 +4105,7 @@
       <c r="O6" s="15"/>
       <c r="P6" s="14"/>
     </row>
-    <row r="7" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4183,14 +4127,14 @@
         <v>75</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I7" s="25"/>
       <c r="J7" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
@@ -4199,7 +4143,7 @@
       <c r="O7" s="15"/>
       <c r="P7" s="14"/>
     </row>
-    <row r="8" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4221,14 +4165,14 @@
         <v>39</v>
       </c>
       <c r="G8" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I8" s="25"/>
       <c r="J8" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
@@ -4237,7 +4181,7 @@
       <c r="O8" s="15"/>
       <c r="P8" s="14"/>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4259,14 +4203,14 @@
         <v>73</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I9" s="25"/>
       <c r="J9" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
@@ -4275,7 +4219,7 @@
       <c r="O9" s="15"/>
       <c r="P9" s="14"/>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4297,14 +4241,14 @@
         <v>68</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I10" s="25"/>
       <c r="J10" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
@@ -4313,7 +4257,7 @@
       <c r="O10" s="15"/>
       <c r="P10" s="14"/>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4335,14 +4279,14 @@
         <v>87</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I11" s="25"/>
       <c r="J11" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
@@ -4351,7 +4295,7 @@
       <c r="O11" s="15"/>
       <c r="P11" s="14"/>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4373,14 +4317,14 @@
         <v>68</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I12" s="24"/>
       <c r="J12" s="9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
@@ -4389,7 +4333,7 @@
       <c r="O12" s="15"/>
       <c r="P12" s="14"/>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4411,14 +4355,14 @@
         <v>67</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I13" s="25"/>
       <c r="J13" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
@@ -4427,7 +4371,7 @@
       <c r="O13" s="15"/>
       <c r="P13" s="14"/>
     </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4449,14 +4393,14 @@
         <v>92</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I14" s="25"/>
       <c r="J14" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
@@ -4465,7 +4409,7 @@
       <c r="O14" s="15"/>
       <c r="P14" s="14"/>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4487,14 +4431,14 @@
         <v>68</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I15" s="25"/>
       <c r="J15" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
@@ -4503,7 +4447,7 @@
       <c r="O15" s="15"/>
       <c r="P15" s="14"/>
     </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4525,14 +4469,14 @@
         <v>55</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I16" s="26"/>
       <c r="J16" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -4541,7 +4485,7 @@
       <c r="O16" s="15"/>
       <c r="P16" s="14"/>
     </row>
-    <row r="17" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4563,14 +4507,14 @@
         <v>71</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I17" s="26"/>
       <c r="J17" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -4579,7 +4523,7 @@
       <c r="O17" s="15"/>
       <c r="P17" s="14"/>
     </row>
-    <row r="18" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4601,14 +4545,14 @@
         <v>63</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I18" s="26"/>
       <c r="J18" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -4617,7 +4561,7 @@
       <c r="O18" s="15"/>
       <c r="P18" s="14"/>
     </row>
-    <row r="19" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4639,14 +4583,14 @@
         <v>77</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I19" s="26"/>
       <c r="J19" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -4655,7 +4599,7 @@
       <c r="O19" s="15"/>
       <c r="P19" s="14"/>
     </row>
-    <row r="20" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4677,14 +4621,14 @@
         <v>74</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I20" s="26"/>
       <c r="J20" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -4693,7 +4637,7 @@
       <c r="O20" s="15"/>
       <c r="P20" s="14"/>
     </row>
-    <row r="21" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4715,14 +4659,14 @@
         <v>168</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I21" s="26"/>
       <c r="J21" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -4731,7 +4675,7 @@
       <c r="O21" s="15"/>
       <c r="P21" s="14"/>
     </row>
-    <row r="22" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4753,14 +4697,14 @@
         <v>159</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I22" s="26"/>
       <c r="J22" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -4769,7 +4713,7 @@
       <c r="O22" s="15"/>
       <c r="P22" s="14"/>
     </row>
-    <row r="23" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4791,14 +4735,14 @@
         <v>136</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I23" s="26"/>
       <c r="J23" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -4807,7 +4751,7 @@
       <c r="O23" s="15"/>
       <c r="P23" s="14"/>
     </row>
-    <row r="24" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4829,14 +4773,14 @@
         <v>78</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I24" s="26"/>
       <c r="J24" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -4845,7 +4789,7 @@
       <c r="O24" s="15"/>
       <c r="P24" s="14"/>
     </row>
-    <row r="25" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4867,14 +4811,14 @@
         <v>80</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I25" s="26"/>
       <c r="J25" s="8" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -4883,7 +4827,7 @@
       <c r="O25" s="15"/>
       <c r="P25" s="14"/>
     </row>
-    <row r="26" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4905,14 +4849,14 @@
         <v>76</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I26" s="26"/>
       <c r="J26" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -4921,7 +4865,7 @@
       <c r="O26" s="15"/>
       <c r="P26" s="14"/>
     </row>
-    <row r="27" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4943,14 +4887,14 @@
         <v>68</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I27" s="26"/>
       <c r="J27" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -4959,7 +4903,7 @@
       <c r="O27" s="15"/>
       <c r="P27" s="14"/>
     </row>
-    <row r="28" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -4981,14 +4925,14 @@
         <v>77</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I28" s="26"/>
       <c r="J28" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -4997,7 +4941,7 @@
       <c r="O28" s="15"/>
       <c r="P28" s="14"/>
     </row>
-    <row r="29" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5019,14 +4963,14 @@
         <v>53</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I29" s="26"/>
       <c r="J29" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -5035,7 +4979,7 @@
       <c r="O29" s="15"/>
       <c r="P29" s="14"/>
     </row>
-    <row r="30" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5057,14 +5001,14 @@
         <v>53</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I30" s="26"/>
       <c r="J30" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -5073,7 +5017,7 @@
       <c r="O30" s="15"/>
       <c r="P30" s="14"/>
     </row>
-    <row r="31" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5095,14 +5039,14 @@
         <v>49</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I31" s="39"/>
       <c r="J31" s="55" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -5111,7 +5055,7 @@
       <c r="O31" s="15"/>
       <c r="P31" s="14"/>
     </row>
-    <row r="32" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5133,16 +5077,16 @@
         <v>57</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I32" s="39">
         <v>1</v>
       </c>
       <c r="J32" s="56" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K32" s="1">
         <v>6</v>
@@ -5159,7 +5103,7 @@
       <c r="O32" s="14"/>
       <c r="P32" s="14"/>
     </row>
-    <row r="33" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5181,14 +5125,14 @@
         <v>44</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I33" s="26"/>
       <c r="J33" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -5197,7 +5141,7 @@
       <c r="O33" s="15"/>
       <c r="P33" s="14"/>
     </row>
-    <row r="34" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5219,14 +5163,14 @@
         <v>68</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I34" s="26"/>
       <c r="J34" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -5235,7 +5179,7 @@
       <c r="O34" s="15"/>
       <c r="P34" s="14"/>
     </row>
-    <row r="35" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5257,14 +5201,14 @@
         <v>64</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I35" s="26"/>
       <c r="J35" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -5273,7 +5217,7 @@
       <c r="O35" s="15"/>
       <c r="P35" s="14"/>
     </row>
-    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5295,14 +5239,14 @@
         <v>55</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I36" s="26"/>
       <c r="J36" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -5311,7 +5255,7 @@
       <c r="O36" s="14"/>
       <c r="P36" s="14"/>
     </row>
-    <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5333,14 +5277,14 @@
         <v>52</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I37" s="39"/>
       <c r="J37" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -5349,7 +5293,7 @@
       <c r="O37" s="14"/>
       <c r="P37" s="14"/>
     </row>
-    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5371,14 +5315,14 @@
         <v>49</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I38" s="39"/>
       <c r="J38" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -5387,7 +5331,7 @@
       <c r="O38" s="14"/>
       <c r="P38" s="14"/>
     </row>
-    <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5409,16 +5353,16 @@
         <v>67</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I39" s="26">
         <v>1</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K39" s="1">
         <v>8</v>
@@ -5434,7 +5378,7 @@
       </c>
       <c r="P39" s="14"/>
     </row>
-    <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5456,14 +5400,14 @@
         <v>53</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I40" s="26"/>
       <c r="J40" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -5472,7 +5416,7 @@
       <c r="O40" s="14"/>
       <c r="P40" s="14"/>
     </row>
-    <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5494,14 +5438,14 @@
         <v>142</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I41" s="26"/>
       <c r="J41" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -5510,7 +5454,7 @@
       <c r="O41" s="14"/>
       <c r="P41" s="14"/>
     </row>
-    <row r="42" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5532,14 +5476,14 @@
         <v>73</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I42" s="26"/>
       <c r="J42" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -5548,7 +5492,7 @@
       <c r="O42" s="14"/>
       <c r="P42" s="14"/>
     </row>
-    <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5570,16 +5514,16 @@
         <v>165</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I43" s="26">
         <v>1</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K43" s="1">
         <v>6</v>
@@ -5596,7 +5540,7 @@
       <c r="O43" s="14"/>
       <c r="P43" s="14"/>
     </row>
-    <row r="44" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5618,14 +5562,14 @@
         <v>200</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I44" s="26"/>
       <c r="J44" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -5634,7 +5578,7 @@
       <c r="O44" s="14"/>
       <c r="P44" s="14"/>
     </row>
-    <row r="45" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5656,14 +5600,14 @@
         <v>200</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I45" s="26"/>
       <c r="J45" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -5672,7 +5616,7 @@
       <c r="O45" s="78"/>
       <c r="P45" s="14"/>
     </row>
-    <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5694,14 +5638,14 @@
         <v>200</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I46" s="26"/>
       <c r="J46" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -5710,7 +5654,7 @@
       <c r="O46" s="14"/>
       <c r="P46" s="14"/>
     </row>
-    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5732,14 +5676,14 @@
         <v>79</v>
       </c>
       <c r="G47" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I47" s="26"/>
       <c r="J47" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -5748,7 +5692,7 @@
       <c r="O47" s="7"/>
       <c r="P47" s="14"/>
     </row>
-    <row r="48" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5770,14 +5714,14 @@
         <v>63</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I48" s="26"/>
       <c r="J48" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -5786,7 +5730,7 @@
       <c r="O48" s="14"/>
       <c r="P48" s="14"/>
     </row>
-    <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="75">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5808,25 +5752,25 @@
         <v>152</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I49" s="27"/>
       <c r="J49" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="30"/>
       <c r="N49" s="33"/>
       <c r="O49" s="85" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="P49" s="14"/>
     </row>
-    <row r="50" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="75">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5848,14 +5792,14 @@
         <v>150</v>
       </c>
       <c r="G50" s="38" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I50" s="27"/>
       <c r="J50" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
@@ -5864,7 +5808,7 @@
       <c r="O50" s="86"/>
       <c r="P50" s="14"/>
     </row>
-    <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5886,14 +5830,14 @@
         <v>141</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I51" s="26"/>
       <c r="J51" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -5902,7 +5846,7 @@
       <c r="O51" s="67"/>
       <c r="P51" s="14"/>
     </row>
-    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5912,7 +5856,7 @@
         <v>13</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D52" s="17">
         <v>46006</v>
@@ -5924,14 +5868,14 @@
         <v>135</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I52" s="10"/>
       <c r="J52" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -5940,7 +5884,7 @@
       <c r="O52" s="67"/>
       <c r="P52" s="14"/>
     </row>
-    <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -5950,7 +5894,7 @@
         <v>13</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D53" s="17">
         <v>46006</v>
@@ -5962,14 +5906,14 @@
         <v>200</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -5978,7 +5922,7 @@
       <c r="O53" s="67"/>
       <c r="P53" s="14"/>
     </row>
-    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6000,14 +5944,14 @@
         <v>137</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -6016,7 +5960,7 @@
       <c r="O54" s="67"/>
       <c r="P54" s="14"/>
     </row>
-    <row r="55" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6038,14 +5982,14 @@
         <v>130</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I55" s="10"/>
       <c r="J55" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -6054,7 +5998,7 @@
       <c r="O55" s="67"/>
       <c r="P55" s="14"/>
     </row>
-    <row r="56" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6076,14 +6020,14 @@
         <v>56</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I56" s="10"/>
       <c r="J56" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -6092,7 +6036,7 @@
       <c r="O56" s="67"/>
       <c r="P56" s="14"/>
     </row>
-    <row r="57" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6114,14 +6058,14 @@
         <v>200</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I57" s="10"/>
       <c r="J57" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -6130,7 +6074,7 @@
       <c r="O57" s="67"/>
       <c r="P57" s="14"/>
     </row>
-    <row r="58" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6152,14 +6096,14 @@
         <v>200</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I58" s="10"/>
       <c r="J58" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -6168,7 +6112,7 @@
       <c r="O58" s="67"/>
       <c r="P58" s="14"/>
     </row>
-    <row r="59" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6190,14 +6134,14 @@
         <v>200</v>
       </c>
       <c r="G59" s="37" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I59" s="10"/>
       <c r="J59" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -6206,7 +6150,7 @@
       <c r="O59" s="67"/>
       <c r="P59" s="14"/>
     </row>
-    <row r="60" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="76">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6228,14 +6172,14 @@
         <v>165</v>
       </c>
       <c r="G60" s="72" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H60" s="68" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I60" s="71"/>
       <c r="J60" s="68" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K60" s="68"/>
       <c r="L60" s="68"/>
@@ -6244,9 +6188,9 @@
       <c r="O60" s="67"/>
       <c r="P60" s="14"/>
     </row>
-    <row r="61" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="80" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B61" s="81"/>
       <c r="C61" s="81"/>
@@ -6263,9 +6207,9 @@
       <c r="N61" s="6"/>
       <c r="O61" s="14"/>
     </row>
-    <row r="62" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="80" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B62" s="82"/>
       <c r="C62" s="82"/>
@@ -6282,9 +6226,9 @@
       <c r="N62" s="28"/>
       <c r="O62" s="14"/>
     </row>
-    <row r="63" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="80" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B63" s="82"/>
       <c r="C63" s="82"/>
@@ -6301,9 +6245,9 @@
       <c r="N63" s="36"/>
       <c r="O63" s="14"/>
     </row>
-    <row r="64" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="83" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B64" s="84"/>
       <c r="C64" s="84"/>
@@ -6320,7 +6264,7 @@
       <c r="N64" s="36"/>
       <c r="O64" s="14"/>
     </row>
-    <row r="65" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F65" s="22"/>
       <c r="I65" s="21">
         <f>SUM(I2:I60)</f>
@@ -6331,55 +6275,55 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H67" s="66"/>
       <c r="I67" s="64"/>
       <c r="J67" s="77"/>
       <c r="M67" s="58"/>
     </row>
-    <row r="68" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H68" s="66"/>
       <c r="I68" s="64"/>
       <c r="J68" s="77"/>
       <c r="M68" s="58"/>
     </row>
-    <row r="69" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H69" s="66"/>
       <c r="I69" s="64"/>
       <c r="J69" s="77"/>
       <c r="M69" s="58"/>
     </row>
-    <row r="70" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H70" s="66"/>
       <c r="I70" s="64"/>
       <c r="J70" s="77"/>
       <c r="M70" s="58"/>
     </row>
-    <row r="71" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H71" s="66"/>
       <c r="I71" s="64"/>
       <c r="J71" s="77"/>
       <c r="M71" s="58"/>
     </row>
-    <row r="72" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H72" s="66"/>
       <c r="I72" s="64"/>
       <c r="J72" s="77"/>
       <c r="M72" s="58"/>
     </row>
-    <row r="73" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H73" s="66"/>
       <c r="I73" s="64"/>
       <c r="J73" s="77"/>
       <c r="M73" s="58"/>
     </row>
-    <row r="74" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H74" s="66"/>
       <c r="I74" s="64"/>
       <c r="J74" s="77"/>
       <c r="M74" s="58"/>
     </row>
-    <row r="75" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="6:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H75" s="65"/>
       <c r="I75" s="64"/>
       <c r="M75" s="58"/>
@@ -6410,24 +6354,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O64"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.42578125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" style="23" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="61" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" style="23" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" style="23" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="23" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="23" customWidth="1"/>
-    <col min="9" max="9" width="6.85546875" style="23" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" style="56" customWidth="1"/>
-    <col min="11" max="12" width="6.42578125" style="23" customWidth="1"/>
-    <col min="13" max="13" width="6.42578125" style="62" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" style="23" customWidth="1"/>
-    <col min="15" max="15" width="9.5703125" customWidth="1"/>
+    <col min="1" max="2" width="6.44140625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" style="23" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="61" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="6.5546875" style="23" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" style="23" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" style="23" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" style="56" customWidth="1"/>
+    <col min="11" max="12" width="6.44140625" style="23" customWidth="1"/>
+    <col min="13" max="13" width="6.44140625" style="62" customWidth="1"/>
+    <col min="14" max="14" width="9.88671875" style="23" customWidth="1"/>
+    <col min="15" max="15" width="9.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="59" t="s">
         <v>0</v>
       </c>
@@ -6472,7 +6416,7 @@
       </c>
       <c r="O1" s="15"/>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="52">
         <v>2026</v>
       </c>
@@ -6492,7 +6436,7 @@
         <v>81</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="24"/>
@@ -6503,7 +6447,7 @@
       <c r="N2" s="34"/>
       <c r="O2" s="15"/>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="53">
         <f>A2</f>
         <v>2026</v>
@@ -6525,7 +6469,7 @@
         <v>85</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="25"/>
@@ -6536,7 +6480,7 @@
       <c r="N3" s="31"/>
       <c r="O3" s="15"/>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="53">
         <f t="shared" ref="A4:B19" si="0">A3</f>
         <v>2026</v>
@@ -6558,7 +6502,7 @@
         <v>73</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="25"/>
@@ -6569,7 +6513,7 @@
       <c r="N4" s="31"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6591,7 +6535,7 @@
         <v>93</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="24"/>
@@ -6602,7 +6546,7 @@
       <c r="N5" s="35"/>
       <c r="O5" s="15"/>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6624,7 +6568,7 @@
         <v>80</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="25"/>
@@ -6635,7 +6579,7 @@
       <c r="N6" s="31"/>
       <c r="O6" s="15"/>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6657,7 +6601,7 @@
         <v>44</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="25"/>
@@ -6668,7 +6612,7 @@
       <c r="N7" s="31"/>
       <c r="O7" s="15"/>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6690,7 +6634,7 @@
         <v>68</v>
       </c>
       <c r="G8" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="25"/>
@@ -6701,7 +6645,7 @@
       <c r="N8" s="31"/>
       <c r="O8" s="15"/>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6723,7 +6667,7 @@
         <v>73</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="25"/>
@@ -6734,7 +6678,7 @@
       <c r="N9" s="31"/>
       <c r="O9" s="15"/>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6756,7 +6700,7 @@
         <v>48</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="25"/>
@@ -6767,7 +6711,7 @@
       <c r="N10" s="31"/>
       <c r="O10" s="15"/>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6789,7 +6733,7 @@
         <v>43</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="25"/>
@@ -6800,7 +6744,7 @@
       <c r="N11" s="31"/>
       <c r="O11" s="15"/>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6822,7 +6766,7 @@
         <v>44</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="24"/>
@@ -6833,7 +6777,7 @@
       <c r="N12" s="35"/>
       <c r="O12" s="15"/>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6855,7 +6799,7 @@
         <v>67</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="25"/>
@@ -6866,7 +6810,7 @@
       <c r="N13" s="31"/>
       <c r="O13" s="15"/>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6882,7 +6826,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="13"/>
       <c r="G14" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="25"/>
@@ -6893,7 +6837,7 @@
       <c r="N14" s="31"/>
       <c r="O14" s="15"/>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6909,7 +6853,7 @@
       <c r="E15" s="8"/>
       <c r="F15" s="13"/>
       <c r="G15" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="25"/>
@@ -6920,7 +6864,7 @@
       <c r="N15" s="31"/>
       <c r="O15" s="15"/>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6936,7 +6880,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="10"/>
       <c r="G16" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="26"/>
@@ -6947,7 +6891,7 @@
       <c r="N16" s="32"/>
       <c r="O16" s="15"/>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6963,7 +6907,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="10"/>
       <c r="G17" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="26"/>
@@ -6974,7 +6918,7 @@
       <c r="N17" s="32"/>
       <c r="O17" s="15"/>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -6990,7 +6934,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="10"/>
       <c r="G18" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="26"/>
@@ -7001,7 +6945,7 @@
       <c r="N18" s="32"/>
       <c r="O18" s="15"/>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="53">
         <f t="shared" si="0"/>
         <v>2026</v>
@@ -7017,7 +6961,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="10"/>
       <c r="G19" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="26"/>
@@ -7028,7 +6972,7 @@
       <c r="N19" s="32"/>
       <c r="O19" s="15"/>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="53">
         <f t="shared" ref="A20:B35" si="1">A19</f>
         <v>2026</v>
@@ -7044,7 +6988,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="10"/>
       <c r="G20" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="26"/>
@@ -7055,7 +6999,7 @@
       <c r="N20" s="32"/>
       <c r="O20" s="15"/>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7071,7 +7015,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="10"/>
       <c r="G21" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="26"/>
@@ -7082,7 +7026,7 @@
       <c r="N21" s="32"/>
       <c r="O21" s="15"/>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7098,7 +7042,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="10"/>
       <c r="G22" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="26"/>
@@ -7109,7 +7053,7 @@
       <c r="N22" s="32"/>
       <c r="O22" s="15"/>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7125,7 +7069,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="10"/>
       <c r="G23" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="26"/>
@@ -7136,7 +7080,7 @@
       <c r="N23" s="32"/>
       <c r="O23" s="15"/>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7152,7 +7096,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="10"/>
       <c r="G24" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="26"/>
@@ -7163,7 +7107,7 @@
       <c r="N24" s="32"/>
       <c r="O24" s="15"/>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7185,7 +7129,7 @@
         <v>33</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="26"/>
@@ -7196,7 +7140,7 @@
       <c r="N25" s="32"/>
       <c r="O25" s="15"/>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7218,7 +7162,7 @@
         <v>19</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="26"/>
@@ -7229,7 +7173,7 @@
       <c r="N26" s="32"/>
       <c r="O26" s="15"/>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7245,7 +7189,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="10"/>
       <c r="G27" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="26"/>
@@ -7256,7 +7200,7 @@
       <c r="N27" s="32"/>
       <c r="O27" s="15"/>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7272,7 +7216,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="10"/>
       <c r="G28" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="26"/>
@@ -7283,7 +7227,7 @@
       <c r="N28" s="32"/>
       <c r="O28" s="15"/>
     </row>
-    <row r="29" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7299,7 +7243,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="10"/>
       <c r="G29" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="26"/>
@@ -7310,7 +7254,7 @@
       <c r="N29" s="32"/>
       <c r="O29" s="15"/>
     </row>
-    <row r="30" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7326,7 +7270,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="10"/>
       <c r="G30" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="26"/>
@@ -7337,7 +7281,7 @@
       <c r="N30" s="32"/>
       <c r="O30" s="15"/>
     </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7353,7 +7297,7 @@
       <c r="E31" s="2"/>
       <c r="F31" s="10"/>
       <c r="G31" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="39"/>
@@ -7364,7 +7308,7 @@
       <c r="N31" s="32"/>
       <c r="O31" s="15"/>
     </row>
-    <row r="32" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7380,7 +7324,7 @@
       <c r="E32" s="2"/>
       <c r="F32" s="10"/>
       <c r="G32" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="39"/>
@@ -7390,7 +7334,7 @@
       <c r="N32" s="32"/>
       <c r="O32" s="14"/>
     </row>
-    <row r="33" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7406,7 +7350,7 @@
       <c r="E33" s="2"/>
       <c r="F33" s="10"/>
       <c r="G33" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="26"/>
@@ -7417,7 +7361,7 @@
       <c r="N33" s="32"/>
       <c r="O33" s="15"/>
     </row>
-    <row r="34" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7433,7 +7377,7 @@
       <c r="E34" s="2"/>
       <c r="F34" s="10"/>
       <c r="G34" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="26"/>
@@ -7444,7 +7388,7 @@
       <c r="N34" s="32"/>
       <c r="O34" s="15"/>
     </row>
-    <row r="35" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="53">
         <f t="shared" si="1"/>
         <v>2026</v>
@@ -7460,7 +7404,7 @@
       <c r="E35" s="2"/>
       <c r="F35" s="10"/>
       <c r="G35" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="26"/>
@@ -7471,7 +7415,7 @@
       <c r="N35" s="32"/>
       <c r="O35" s="15"/>
     </row>
-    <row r="36" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <f t="shared" ref="A36:B51" si="2">A35</f>
         <v>2026</v>
@@ -7487,7 +7431,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="10"/>
       <c r="G36" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="26"/>
@@ -7498,7 +7442,7 @@
       <c r="N36" s="32"/>
       <c r="O36" s="14"/>
     </row>
-    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7514,7 +7458,7 @@
       <c r="E37" s="2"/>
       <c r="F37" s="10"/>
       <c r="G37" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="39"/>
@@ -7525,7 +7469,7 @@
       <c r="N37" s="32"/>
       <c r="O37" s="14"/>
     </row>
-    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7541,7 +7485,7 @@
       <c r="E38" s="2"/>
       <c r="F38" s="10"/>
       <c r="G38" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="39"/>
@@ -7552,7 +7496,7 @@
       <c r="N38" s="32"/>
       <c r="O38" s="14"/>
     </row>
-    <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7568,7 +7512,7 @@
       <c r="E39" s="2"/>
       <c r="F39" s="10"/>
       <c r="G39" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="26"/>
@@ -7578,7 +7522,7 @@
       <c r="M39" s="29"/>
       <c r="N39" s="32"/>
     </row>
-    <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7594,7 +7538,7 @@
       <c r="E40" s="2"/>
       <c r="F40" s="10"/>
       <c r="G40" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="26"/>
@@ -7605,7 +7549,7 @@
       <c r="N40" s="32"/>
       <c r="O40" s="14"/>
     </row>
-    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7621,7 +7565,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="10"/>
       <c r="G41" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="26"/>
@@ -7632,7 +7576,7 @@
       <c r="N41" s="32"/>
       <c r="O41" s="14"/>
     </row>
-    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7648,7 +7592,7 @@
       <c r="E42" s="2"/>
       <c r="F42" s="10"/>
       <c r="G42" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="26"/>
@@ -7659,7 +7603,7 @@
       <c r="N42" s="32"/>
       <c r="O42" s="14"/>
     </row>
-    <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7675,7 +7619,7 @@
       <c r="E43" s="2"/>
       <c r="F43" s="10"/>
       <c r="G43" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="26"/>
@@ -7686,7 +7630,7 @@
       <c r="N43" s="32"/>
       <c r="O43" s="14"/>
     </row>
-    <row r="44" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7702,7 +7646,7 @@
       <c r="E44" s="2"/>
       <c r="F44" s="10"/>
       <c r="G44" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="26"/>
@@ -7713,7 +7657,7 @@
       <c r="N44" s="32"/>
       <c r="O44" s="14"/>
     </row>
-    <row r="45" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7729,7 +7673,7 @@
       <c r="E45" s="2"/>
       <c r="F45" s="10"/>
       <c r="G45" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="26"/>
@@ -7740,7 +7684,7 @@
       <c r="N45" s="32"/>
       <c r="O45" s="78"/>
     </row>
-    <row r="46" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7756,7 +7700,7 @@
       <c r="E46" s="2"/>
       <c r="F46" s="10"/>
       <c r="G46" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="26"/>
@@ -7767,7 +7711,7 @@
       <c r="N46" s="32"/>
       <c r="O46" s="14"/>
     </row>
-    <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7783,7 +7727,7 @@
       <c r="E47" s="2"/>
       <c r="F47" s="10"/>
       <c r="G47" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="26"/>
@@ -7794,7 +7738,7 @@
       <c r="N47" s="32"/>
       <c r="O47" s="7"/>
     </row>
-    <row r="48" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7810,7 +7754,7 @@
       <c r="E48" s="2"/>
       <c r="F48" s="10"/>
       <c r="G48" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="26"/>
@@ -7821,7 +7765,7 @@
       <c r="N48" s="32"/>
       <c r="O48" s="14"/>
     </row>
-    <row r="49" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="75">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7843,7 +7787,7 @@
         <v>25</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="27"/>
@@ -7853,10 +7797,10 @@
       <c r="M49" s="30"/>
       <c r="N49" s="33"/>
       <c r="O49" s="85" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="75">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7878,7 +7822,7 @@
         <v>15</v>
       </c>
       <c r="G50" s="38" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="27"/>
@@ -7889,7 +7833,7 @@
       <c r="N50" s="33"/>
       <c r="O50" s="86"/>
     </row>
-    <row r="51" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="53">
         <f t="shared" si="2"/>
         <v>2026</v>
@@ -7911,7 +7855,7 @@
         <v>19</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="26"/>
@@ -7922,7 +7866,7 @@
       <c r="N51" s="32"/>
       <c r="O51" s="67"/>
     </row>
-    <row r="52" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="53">
         <f t="shared" ref="A52:B60" si="3">A51</f>
         <v>2026</v>
@@ -7944,7 +7888,7 @@
         <v>30</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="10"/>
@@ -7955,7 +7899,7 @@
       <c r="N52" s="32"/>
       <c r="O52" s="67"/>
     </row>
-    <row r="53" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="53">
         <f t="shared" si="3"/>
         <v>2026</v>
@@ -7977,7 +7921,7 @@
         <v>200</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="10"/>
@@ -7988,7 +7932,7 @@
       <c r="N53" s="32"/>
       <c r="O53" s="67"/>
     </row>
-    <row r="54" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="53">
         <f t="shared" si="3"/>
         <v>2026</v>
@@ -8010,7 +7954,7 @@
         <v>60</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="10"/>
@@ -8021,7 +7965,7 @@
       <c r="N54" s="32"/>
       <c r="O54" s="67"/>
     </row>
-    <row r="55" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="53">
         <f t="shared" si="3"/>
         <v>2026</v>
@@ -8043,7 +7987,7 @@
         <v>95</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="10"/>
@@ -8054,7 +7998,7 @@
       <c r="N55" s="32"/>
       <c r="O55" s="67"/>
     </row>
-    <row r="56" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="53">
         <f t="shared" si="3"/>
         <v>2026</v>
@@ -8076,7 +8020,7 @@
         <v>78</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="10"/>
@@ -8087,7 +8031,7 @@
       <c r="N56" s="32"/>
       <c r="O56" s="67"/>
     </row>
-    <row r="57" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="53">
         <f t="shared" si="3"/>
         <v>2026</v>
@@ -8109,7 +8053,7 @@
         <v>200</v>
       </c>
       <c r="G57" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="10"/>
@@ -8120,7 +8064,7 @@
       <c r="N57" s="32"/>
       <c r="O57" s="67"/>
     </row>
-    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="53">
         <f t="shared" si="3"/>
         <v>2026</v>
@@ -8142,7 +8086,7 @@
         <v>155</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="10"/>
@@ -8153,7 +8097,7 @@
       <c r="N58" s="32"/>
       <c r="O58" s="67"/>
     </row>
-    <row r="59" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="53">
         <f t="shared" si="3"/>
         <v>2026</v>
@@ -8169,7 +8113,7 @@
       <c r="E59" s="2"/>
       <c r="F59" s="10"/>
       <c r="G59" s="37" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="10"/>
@@ -8180,7 +8124,7 @@
       <c r="N59" s="32"/>
       <c r="O59" s="67"/>
     </row>
-    <row r="60" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="76">
         <f t="shared" si="3"/>
         <v>2026</v>
@@ -8202,7 +8146,7 @@
         <v>24</v>
       </c>
       <c r="G60" s="72" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H60" s="68"/>
       <c r="I60" s="71"/>
@@ -8213,9 +8157,9 @@
       <c r="N60" s="74"/>
       <c r="O60" s="67"/>
     </row>
-    <row r="61" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="80" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B61" s="81"/>
       <c r="C61" s="81"/>
@@ -8232,9 +8176,9 @@
       <c r="N61" s="6"/>
       <c r="O61" s="14"/>
     </row>
-    <row r="62" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="80" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B62" s="82"/>
       <c r="C62" s="82"/>
@@ -8251,9 +8195,9 @@
       <c r="N62" s="28"/>
       <c r="O62" s="14"/>
     </row>
-    <row r="63" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="80" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B63" s="82"/>
       <c r="C63" s="82"/>
@@ -8270,9 +8214,9 @@
       <c r="N63" s="36"/>
       <c r="O63" s="14"/>
     </row>
-    <row r="64" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="83" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B64" s="84"/>
       <c r="C64" s="84"/>
@@ -8312,7 +8256,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F45CF7A5-F33A-49E5-BAC0-007F8DC3EEB1}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8321,11 +8265,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52214ECD-0667-40E8-BCA3-C8D1AEBD3478}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="24.6" x14ac:dyDescent="0.4">
       <c r="A1" s="87" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B1" s="87"/>
       <c r="C1" s="87"/>
@@ -8338,7 +8282,7 @@
       <c r="J1" s="87"/>
       <c r="K1" s="87"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N2" s="79"/>
     </row>
   </sheetData>
